--- a/inst/resources/variable_schema_data_household_template.xlsx
+++ b/inst/resources/variable_schema_data_household_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\Positron\public_health_resources\inst\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4D9823B-F4A3-4D13-948C-63174DA3034F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42A92279-E358-469F-8E42-9A8931ECE687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42179,59 +42179,59 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B762:B813">
+    <cfRule type="duplicateValues" dxfId="17" priority="30"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C756:C759 C762:C764">
-    <cfRule type="duplicateValues" dxfId="17" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C766:C768">
-    <cfRule type="duplicateValues" dxfId="16" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C770:C772 C774:C779">
+    <cfRule type="duplicateValues" dxfId="14" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J762:J773">
-    <cfRule type="duplicateValues" dxfId="15" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J774:J776">
+    <cfRule type="duplicateValues" dxfId="12" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J777:J779">
+    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J780:J781">
-    <cfRule type="duplicateValues" dxfId="14" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J795:J797 J800">
-    <cfRule type="duplicateValues" dxfId="13" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J798">
-    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J799">
-    <cfRule type="duplicateValues" dxfId="11" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J801:J802">
-    <cfRule type="duplicateValues" dxfId="10" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J804">
-    <cfRule type="duplicateValues" dxfId="9" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J805">
-    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J807">
-    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J808">
-    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J810:J813">
-    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P742:P754">
-    <cfRule type="duplicateValues" dxfId="4" priority="27"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B762:B813">
-    <cfRule type="duplicateValues" dxfId="3" priority="30"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C770:C772 C774:C779">
-    <cfRule type="duplicateValues" dxfId="2" priority="32"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J774:J776">
-    <cfRule type="duplicateValues" dxfId="1" priority="34"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J777:J779">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/inst/resources/variable_schema_data_household_template.xlsx
+++ b/inst/resources/variable_schema_data_household_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\Positron\public_health_resources\inst\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECEF81E4-642D-47FE-82BD-8662DD7FC9D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E548C446-CF49-4906-A985-68DA19905A08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14505" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23520" yWindow="675" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9661" uniqueCount="2071">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9671" uniqueCount="2075">
   <si>
     <t>rule_type</t>
   </si>
@@ -6233,6 +6233,18 @@
   </si>
   <si>
     <t>linked_roster_2to5,num_children_2_5yr</t>
+  </si>
+  <si>
+    <t>linked_death_months</t>
+  </si>
+  <si>
+    <t>linked_birth_months</t>
+  </si>
+  <si>
+    <t>linked_roster_birth_months</t>
+  </si>
+  <si>
+    <t>linked_deaths_death_month</t>
   </si>
 </sst>
 </file>
@@ -6753,7 +6765,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S814"/>
+  <dimension ref="A1:S816"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="37.140625" customWidth="1"/>
@@ -42258,60 +42270,106 @@
         <v>2002</v>
       </c>
     </row>
+    <row r="815" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A815" t="s">
+        <v>1</v>
+      </c>
+      <c r="B815" t="s">
+        <v>2072</v>
+      </c>
+      <c r="D815">
+        <v>0</v>
+      </c>
+      <c r="E815" t="s">
+        <v>20</v>
+      </c>
+      <c r="F815" t="s">
+        <v>66</v>
+      </c>
+      <c r="G815" t="b">
+        <v>0</v>
+      </c>
+      <c r="J815" t="s">
+        <v>2073</v>
+      </c>
+    </row>
+    <row r="816" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A816" t="s">
+        <v>1</v>
+      </c>
+      <c r="B816" t="s">
+        <v>2071</v>
+      </c>
+      <c r="D816">
+        <v>0</v>
+      </c>
+      <c r="E816" t="s">
+        <v>20</v>
+      </c>
+      <c r="F816" t="s">
+        <v>66</v>
+      </c>
+      <c r="G816" t="b">
+        <v>0</v>
+      </c>
+      <c r="J816" t="s">
+        <v>2074</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B763:B814">
-    <cfRule type="duplicateValues" dxfId="17" priority="30"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C757:C760 C763:C765">
-    <cfRule type="duplicateValues" dxfId="16" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C767:C769">
-    <cfRule type="duplicateValues" dxfId="15" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C771:C773 C775:C780">
-    <cfRule type="duplicateValues" dxfId="14" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J763:J774">
-    <cfRule type="duplicateValues" dxfId="13" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J775:J777">
-    <cfRule type="duplicateValues" dxfId="12" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J778:J780">
-    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J781:J782">
-    <cfRule type="duplicateValues" dxfId="10" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J796:J798 J801">
-    <cfRule type="duplicateValues" dxfId="9" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J799">
-    <cfRule type="duplicateValues" dxfId="8" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J800">
-    <cfRule type="duplicateValues" dxfId="7" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J802:J803">
-    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J805">
-    <cfRule type="duplicateValues" dxfId="5" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J806">
-    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J808">
-    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J809">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J811:J814">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  <conditionalFormatting sqref="J811:J815">
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P743:P755">
-    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B763:B816">
+    <cfRule type="duplicateValues" dxfId="0" priority="35"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
